--- a/Result/profitability/5328.xlsx
+++ b/Result/profitability/5328.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.35</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05875</v>
+        <v>0.08875</v>
       </c>
       <c r="N2" t="n">
-        <v>24.5825</v>
+        <v>24.38375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05749999999999999</v>
+        <v>0.05999999999999998</v>
       </c>
       <c r="N3" t="n">
-        <v>22.68625</v>
+        <v>22.35375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.44</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07874999999999999</v>
+        <v>0.10875</v>
       </c>
       <c r="N4" t="n">
-        <v>20.13</v>
+        <v>19.97625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.06624999999999998</v>
+        <v>0.09874999999999998</v>
       </c>
       <c r="N5" t="n">
-        <v>18.87875</v>
+        <v>18.33125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07624999999999998</v>
+        <v>0.09624999999999997</v>
       </c>
       <c r="N6" t="n">
-        <v>16.90125</v>
+        <v>16.76</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05624999999999998</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>17.41875</v>
+        <v>16.8325</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.03</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02999999999999999</v>
+        <v>0.05249999999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>16.54625</v>
+        <v>16.73375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5328</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>290</v>
+      </c>
+      <c r="D75" t="n">
+        <v>219</v>
+      </c>
+      <c r="E75" t="n">
+        <v>71</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="G75" t="n">
+        <v>15</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.05%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>52</v>
+      </c>
+      <c r="J75" t="n">
+        <v>67</v>
+      </c>
+      <c r="K75" t="n">
+        <v>50</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.13875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>26.2125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.636363636363636</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.06538796861377505</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>8.666666666666666</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.379999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1519777931991672</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
